--- a/data/trans_camb/P1417-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1417-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,13</t>
+          <t>3,88</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,69</t>
+          <t>2,12</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,3</t>
+          <t>-1,67; 1,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,97</t>
+          <t>-1,38; 1,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 1,52</t>
+          <t>-1,49; 1,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 5,89</t>
+          <t>0,73; 5,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 4,94</t>
+          <t>0,57; 4,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,63; 11,07</t>
+          <t>1,87; 7,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,9</t>
+          <t>0,17; 2,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 3,03</t>
+          <t>0,07; 2,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 5,81</t>
+          <t>0,87; 3,78</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1247,0%</t>
+          <t>942,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>535,26%</t>
+          <t>421,78%</t>
         </is>
       </c>
     </row>
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-31,22; —</t>
+          <t>-35,39; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-57,55; —</t>
+          <t>-46,67; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,27; —</t>
+          <t>2,74; —</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,83</t>
+          <t>1,6</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,11</t>
+          <t>1,02</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 0,0</t>
+          <t>-1,77; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,52</t>
+          <t>-0,66; 1,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,42</t>
+          <t>-0,72; 1,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 1,61</t>
+          <t>-1,96; 1,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 0,1</t>
+          <t>-2,96; 0,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 3,71</t>
+          <t>-0,3; 3,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,66</t>
+          <t>-1,2; 0,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,37</t>
+          <t>-1,38; 0,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,18</t>
+          <t>-0,07; 2,03</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>115,27%</t>
+          <t>115,56%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>80,04%</t>
         </is>
       </c>
     </row>
@@ -1014,32 +1014,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-65,81; 138,64</t>
+          <t>-64,0; 117,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-91,62; 31,8</t>
+          <t>-91,73; 31,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 292,28</t>
+          <t>-15,29; 254,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-69,75; 99,85</t>
+          <t>-66,53; 95,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-78,3; 59,28</t>
+          <t>-75,13; 80,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 268,4</t>
+          <t>-7,53; 263,34</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,47</t>
+          <t>2,51</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,85</t>
+          <t>1,88</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,12</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,24</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,54</t>
+          <t>0,41; 2,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 2,81</t>
+          <t>-0,7; 2,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 3,0</t>
+          <t>-0,62; 3,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,35</t>
+          <t>0,9; 4,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 1,97</t>
+          <t>-0,13; 1,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 1,79</t>
+          <t>-0,23; 1,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,9</t>
+          <t>0,95; 2,91</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>284,95%</t>
+          <t>289,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>416,7%</t>
+          <t>423,54%</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-62,81; 1038,38</t>
+          <t>-63,94; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-55,42; inf</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,0; 1562,33</t>
+          <t>20,64; 1493,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-29,95; —</t>
+          <t>-61,16; 1117,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,1; 1232,12</t>
+          <t>-58,44; 1043,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>50,62; 1982,17</t>
+          <t>52,89; 2001,17</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,99</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,35</t>
+          <t>3,19</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,9</t>
+          <t>2,19</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,0</t>
+          <t>-1,42; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 2,22</t>
+          <t>-0,25; 2,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 2,15</t>
+          <t>0,08; 2,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,32</t>
+          <t>0,79; 5,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 5,32</t>
+          <t>0,54; 5,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,65</t>
+          <t>1,3; 5,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,65</t>
+          <t>0,17; 2,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,06</t>
+          <t>0,56; 3,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,27</t>
+          <t>1,11; 3,54</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>375,74%</t>
+          <t>383,67%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>191,1%</t>
+          <t>259,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>251,94%</t>
+          <t>289,89%</t>
         </is>
       </c>
     </row>
@@ -1446,32 +1446,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,25; 922,37</t>
+          <t>21,47; 1009,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,88; 992,5</t>
+          <t>-3,37; 802,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,63; 979,09</t>
+          <t>36,53; 1330,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,39; 833,12</t>
+          <t>3,47; 766,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>35,0; 858,36</t>
+          <t>23,4; 869,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>28,88; 887,86</t>
+          <t>68,41; 1023,7</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,16</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,21</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,21</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 4,05</t>
+          <t>-0,31; 3,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,4</t>
+          <t>-0,81; 1,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,13</t>
+          <t>-1,19; 1,01</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 6,67</t>
+          <t>-1,39; 6,65</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 2,89</t>
+          <t>-3,61; 3,1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 2,93</t>
+          <t>-2,94; 2,79</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 4,32</t>
+          <t>-0,41; 4,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 1,63</t>
+          <t>-1,83; 1,74</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 1,68</t>
+          <t>-1,62; 1,66</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -1662,32 +1662,32 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-52,38; 404,43</t>
+          <t>-39,71; 462,59</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-72,6; 276,09</t>
+          <t>-78,86; 225,18</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-58,81; 266,36</t>
+          <t>-58,44; 221,34</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-19,32; 499,71</t>
+          <t>-27,39; 460,83</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-71,52; 206,53</t>
+          <t>-69,7; 227,27</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-54,27; 197,91</t>
+          <t>-53,58; 213,78</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3,63</t>
+          <t>3,58</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,55</t>
+          <t>4,38</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4,06</t>
+          <t>3,96</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,48</t>
+          <t>0,0; 2,57</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,12</t>
+          <t>0,3; 3,23</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,69</t>
+          <t>2,17; 5,6</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 2,75</t>
+          <t>-1,17; 2,52</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 2,82</t>
+          <t>-1,21; 2,65</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,17; 7,16</t>
+          <t>2,05; 6,7</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,95</t>
+          <t>-0,22; 1,98</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 2,04</t>
+          <t>-0,22; 2,16</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2,76; 5,65</t>
+          <t>2,73; 5,64</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>412,42%</t>
+          <t>396,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>726,02%</t>
+          <t>708,1%</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-83,23; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-80,48; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>67,45; —</t>
+          <t>56,19; 1604,9</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-55,34; 932,14</t>
+          <t>-44,78; 1255,75</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-55,76; 949,58</t>
+          <t>-58,0; 1093,98</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>190,03; 2905,89</t>
+          <t>200,88; inf</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>1,46</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,13</t>
+          <t>6,61</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3,0</t>
+          <t>4,15</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,32</t>
+          <t>-1,12; 0,33</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,5</t>
+          <t>-0,98; 0,51</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,25</t>
+          <t>0,28; 2,79</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 2,52</t>
+          <t>-1,46; 2,37</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 2,42</t>
+          <t>-1,27; 2,32</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 6,91</t>
+          <t>4,38; 8,91</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 1,16</t>
+          <t>-0,92; 1,18</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,19</t>
+          <t>-0,83; 1,22</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,44</t>
+          <t>2,71; 5,45</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>197,38%</t>
+          <t>250,33%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>165,86%</t>
+          <t>265,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>192,9%</t>
+          <t>266,83%</t>
         </is>
       </c>
     </row>
@@ -2089,37 +2089,37 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-16,49; 1024,3</t>
+          <t>-4,4; 1066,15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-42,14; 159,77</t>
+          <t>-45,24; 150,11</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-36,7; 156,53</t>
+          <t>-38,72; 151,0</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,85; 373,81</t>
+          <t>106,1; 603,18</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-48,44; 123,29</t>
+          <t>-44,87; 115,48</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-38,83; 124,84</t>
+          <t>-38,95; 116,23</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>56,95; 411,05</t>
+          <t>111,34; 517,94</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-0,37</t>
+          <t>-0,29</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>-0,22</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-0,38</t>
+          <t>-0,26</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,68</t>
+          <t>-0,92; 0,69</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,3; -0,01</t>
+          <t>-1,18; 0,01</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,18</t>
+          <t>-1,04; 0,36</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,82</t>
+          <t>-0,8; 1,77</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 2,43</t>
+          <t>-0,47; 2,49</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 0,86</t>
+          <t>-1,41; 0,93</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,94</t>
+          <t>-0,61; 0,97</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,06</t>
+          <t>-0,54; 1,04</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,27</t>
+          <t>-1,01; 0,38</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-57,7%</t>
+          <t>-44,76%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-12,59%</t>
+          <t>-13,5%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-32,65%</t>
+          <t>-22,24%</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-85,67; 292,4</t>
+          <t>-88,73; 310,36</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2305,37 +2305,37 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 154,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-45,64; 184,26</t>
+          <t>-42,49; 166,12</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-21,36; 230,3</t>
+          <t>-23,76; 254,07</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-65,99; 103,31</t>
+          <t>-57,98; 98,04</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-37,79; 131,24</t>
+          <t>-41,15; 125,72</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-37,56; 142,03</t>
+          <t>-39,38; 145,21</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-71,32; 33,79</t>
+          <t>-62,84; 55,1</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,48</t>
+          <t>2,81</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1,63</t>
+          <t>1,86</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,32</t>
+          <t>-0,29; 0,36</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,49</t>
+          <t>-0,21; 0,5</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,1</t>
+          <t>0,45; 1,2</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,72</t>
+          <t>0,29; 1,72</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,5</t>
+          <t>0,06; 1,43</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,37</t>
+          <t>2,06; 3,58</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,91</t>
+          <t>0,16; 0,95</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,87</t>
+          <t>0,07; 0,88</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,07</t>
+          <t>1,44; 2,3</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>172,7%</t>
+          <t>201,49%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>145,44%</t>
+          <t>164,76%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>152,42%</t>
+          <t>173,61%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-54,6; 128,77</t>
+          <t>-52,01; 141,41</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-34,42; 186,55</t>
+          <t>-41,02; 184,86</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>39,29; 445,22</t>
+          <t>62,96; 473,84</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>14,85; 122,3</t>
+          <t>12,48; 121,35</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>6,4; 111,45</t>
+          <t>1,59; 103,78</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>76,31; 246,6</t>
+          <t>100,35; 265,53</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>7,66; 102,72</t>
+          <t>11,62; 104,37</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>4,58; 97,22</t>
+          <t>6,17; 97,85</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>88,57; 234,71</t>
+          <t>108,79; 262,21</t>
         </is>
       </c>
     </row>
